--- a/SGC-CKN/Excel/115c95f2-795b-4d88-bd79-4e58775f2f30_Lô_CT-02_P1-110_D800_07-04-2026.xlsx
+++ b/SGC-CKN/Excel/115c95f2-795b-4d88-bd79-4e58775f2f30_Lô_CT-02_P1-110_D800_07-04-2026.xlsx
@@ -349,17 +349,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFDE68A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -380,6 +375,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9F99D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -520,44 +520,44 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1169,7 +1169,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-0.67</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-1.27</v>
@@ -1178,10 +1178,10 @@
         <v>0.2</v>
       </c>
       <c r="I11" s="5">
-        <v>0.6</v>
+        <v>1.27</v>
       </c>
       <c r="J11" s="8">
-        <v>3</v>
+        <v>6.35</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1215,7 +1215,7 @@
       <c r="I12" s="9">
         <v>3.1</v>
       </c>
-      <c r="J12" s="12">
+      <c r="J12" s="8">
         <v>8.86</v>
       </c>
       <c r="K12" s="10" t="s">
@@ -1223,142 +1223,142 @@
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="12">
         <v>-4.37</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="12">
         <v>-7.67</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="12">
         <v>0.52</v>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="12">
         <v>3.3</v>
       </c>
-      <c r="J13" s="12">
+      <c r="J13" s="8">
         <v>6.39</v>
       </c>
-      <c r="K13" s="14" t="s">
+      <c r="K13" s="13" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="15">
         <v>-7.67</v>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="15">
         <v>-16.47</v>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="15">
         <v>0.97</v>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="15">
         <v>8.8</v>
       </c>
-      <c r="J14" s="12">
+      <c r="J14" s="8">
         <v>9.1</v>
       </c>
-      <c r="K14" s="17" t="s">
+      <c r="K14" s="16" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="D15" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="E15" s="21" t="s">
+      <c r="E15" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="19">
+      <c r="F15" s="18">
         <v>-16.47</v>
       </c>
-      <c r="G15" s="19">
+      <c r="G15" s="18">
         <v>-21.67</v>
       </c>
-      <c r="H15" s="19">
+      <c r="H15" s="18">
         <v>0.62</v>
       </c>
-      <c r="I15" s="19">
+      <c r="I15" s="18">
         <v>5.2</v>
       </c>
-      <c r="J15" s="12">
+      <c r="J15" s="8">
         <v>8.43</v>
       </c>
-      <c r="K15" s="20" t="s">
+      <c r="K15" s="19" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="D16" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E16" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="F16" s="22">
+      <c r="F16" s="21">
         <v>-21.67</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="21">
         <v>-25.67</v>
       </c>
-      <c r="H16" s="22">
+      <c r="H16" s="21">
         <v>0.8</v>
       </c>
-      <c r="I16" s="22">
+      <c r="I16" s="21">
         <v>4</v>
       </c>
-      <c r="J16" s="8">
+      <c r="J16" s="24">
         <v>5</v>
       </c>
-      <c r="K16" s="23" t="s">
+      <c r="K16" s="22" t="s">
         <v>50</v>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       <c r="I17" s="25">
         <v>13.63</v>
       </c>
-      <c r="J17" s="8">
+      <c r="J17" s="24">
         <v>2.98</v>
       </c>
       <c r="K17" s="26" t="s">
@@ -1425,7 +1425,7 @@
       <c r="I18" s="28">
         <v>5.23</v>
       </c>
-      <c r="J18" s="8">
+      <c r="J18" s="24">
         <v>1.52</v>
       </c>
       <c r="K18" s="29" t="s">
@@ -1581,7 +1581,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-0.67</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-1.27</v>
@@ -1590,10 +1590,10 @@
         <v>0.2</v>
       </c>
       <c r="H2" s="5">
-        <v>0.6</v>
+        <v>1.27</v>
       </c>
       <c r="I2" s="8">
-        <v>3</v>
+        <v>6.35</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1621,123 +1621,123 @@
       <c r="H3" s="9">
         <v>3.1</v>
       </c>
-      <c r="I3" s="12">
+      <c r="I3" s="8">
         <v>8.86</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
+      <c r="A4" s="12">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="12">
         <v>1</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="12">
         <v>-4.37</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="12">
         <v>-7.67</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="12">
         <v>0.52</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="12">
         <v>3.3</v>
       </c>
-      <c r="I4" s="12">
+      <c r="I4" s="8">
         <v>6.39</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="16">
+      <c r="A5" s="15">
         <v>4</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="15">
         <v>1</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="15">
         <v>-7.67</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="15">
         <v>-16.47</v>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="15">
         <v>0.97</v>
       </c>
-      <c r="H5" s="16">
+      <c r="H5" s="15">
         <v>8.8</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="8">
         <v>9.1</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="19">
+      <c r="A6" s="18">
         <v>5</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="18">
         <v>1</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="18">
         <v>-16.47</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="18">
         <v>-21.67</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="18">
         <v>0.62</v>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="18">
         <v>5.2</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="8">
         <v>8.43</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="22">
+      <c r="A7" s="21">
         <v>6</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="21">
         <v>1</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="21">
         <v>-21.67</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="21">
         <v>-25.67</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="21">
         <v>0.8</v>
       </c>
-      <c r="H7" s="22">
+      <c r="H7" s="21">
         <v>4</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="24">
         <v>5</v>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       <c r="H8" s="25">
         <v>13.63</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="24">
         <v>2.98</v>
       </c>
     </row>
@@ -1795,7 +1795,7 @@
       <c r="H9" s="28">
         <v>5.23</v>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="24">
         <v>1.52</v>
       </c>
     </row>
@@ -1813,7 +1813,7 @@
         <v>8</v>
       </c>
       <c r="E10" s="33">
-        <v>-0.67</v>
+        <v>0</v>
       </c>
       <c r="F10" s="33">
         <v>-44.53</v>
@@ -1822,10 +1822,10 @@
         <v>11.45</v>
       </c>
       <c r="H10" s="33">
-        <v>43.86</v>
+        <v>44.53</v>
       </c>
       <c r="I10" s="33">
-        <v>3.83</v>
+        <v>3.89</v>
       </c>
     </row>
   </sheetData>
